--- a/artfynd/A 46201-2023 artfynd.xlsx
+++ b/artfynd/A 46201-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3273,6 +3273,108 @@
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>121672277</v>
+      </c>
+      <c r="B27" t="n">
+        <v>95657</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>53</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Gruvhöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>343908</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6617778</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Eda</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Köla</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-10-31</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-10-31</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Anders Boström</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Anders Boström</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 46201-2023 artfynd.xlsx
+++ b/artfynd/A 46201-2023 artfynd.xlsx
@@ -3278,7 +3278,7 @@
         <v>121672277</v>
       </c>
       <c r="B27" t="n">
-        <v>95660</v>
+        <v>95678</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>

--- a/artfynd/A 46201-2023 artfynd.xlsx
+++ b/artfynd/A 46201-2023 artfynd.xlsx
@@ -3278,7 +3278,7 @@
         <v>121672277</v>
       </c>
       <c r="B27" t="n">
-        <v>95678</v>
+        <v>95680</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>

--- a/artfynd/A 46201-2023 artfynd.xlsx
+++ b/artfynd/A 46201-2023 artfynd.xlsx
@@ -3278,7 +3278,7 @@
         <v>121672277</v>
       </c>
       <c r="B27" t="n">
-        <v>95680</v>
+        <v>95687</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
